--- a/vatsAi/bulkusers.upload/temp/samplefile.xlsx
+++ b/vatsAi/bulkusers.upload/temp/samplefile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAPTOP\Desktop\Auth-GridList (2)\Auth-GridList\vatsAi\bulkusers.upload\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A86C6B-EB82-4BA2-ABB0-8B3A3442CB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD2D81E-1842-45F1-B727-620271D0C517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="94">
   <si>
     <t>fullName</t>
   </si>
@@ -213,18 +213,6 @@
     <t>123 Street 2, City</t>
   </si>
   <si>
-    <t>candidate3@test.com</t>
-  </si>
-  <si>
-    <t>9876543202</t>
-  </si>
-  <si>
-    <t>123 Street 3, City</t>
-  </si>
-  <si>
-    <t>Quantum Astrology</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -249,15 +237,6 @@
     <t>123 Street 5, City</t>
   </si>
   <si>
-    <t>candidate6@test.com</t>
-  </si>
-  <si>
-    <t>9876543205</t>
-  </si>
-  <si>
-    <t>123 Street 6, City</t>
-  </si>
-  <si>
     <t>9876543206</t>
   </si>
   <si>
@@ -267,36 +246,6 @@
     <t>Ad 2 (Designer)</t>
   </si>
   <si>
-    <t>candidate8@test.com</t>
-  </si>
-  <si>
-    <t>9876543207</t>
-  </si>
-  <si>
-    <t>123 Street 8, City</t>
-  </si>
-  <si>
-    <t>candidate9@test.com</t>
-  </si>
-  <si>
-    <t>9876543208</t>
-  </si>
-  <si>
-    <t>123 Street 9, City</t>
-  </si>
-  <si>
-    <t>Ad 1 (Developer), Ad 2 (Designer)</t>
-  </si>
-  <si>
-    <t>candidate10@test.com</t>
-  </si>
-  <si>
-    <t>9876543209</t>
-  </si>
-  <si>
-    <t>123 Street 10, City</t>
-  </si>
-  <si>
     <t>bit2bite124@gmail.com</t>
   </si>
   <si>
@@ -318,70 +267,46 @@
     <t>Ram</t>
   </si>
   <si>
-    <t>Lakshman</t>
-  </si>
-  <si>
     <t>sita</t>
   </si>
   <si>
     <t>Gitanjali</t>
   </si>
   <si>
-    <t>kriti</t>
-  </si>
-  <si>
     <t>suketu</t>
   </si>
   <si>
-    <t>eklavya</t>
-  </si>
-  <si>
-    <t>arjun</t>
-  </si>
-  <si>
-    <t>sara</t>
-  </si>
-  <si>
     <t>shekhavatsinh</t>
   </si>
   <si>
     <t>bahadursinh</t>
   </si>
   <si>
-    <t>kirpanbhai</t>
-  </si>
-  <si>
     <t>sumerubhai</t>
   </si>
   <si>
     <t>bhavaniptrabhai</t>
   </si>
   <si>
-    <t>ravbabhau</t>
-  </si>
-  <si>
     <t>meelindbhai</t>
   </si>
   <si>
-    <t>shyambhai</t>
-  </si>
-  <si>
-    <t>ketanbhai</t>
-  </si>
-  <si>
-    <t>lalitbhai</t>
-  </si>
-  <si>
     <t>https://i.pinimg.com/736x/78/c8/fc/78c8fc5f0a3904203b0f4ebba888e169.jpg</t>
   </si>
   <si>
-    <t>https://i.pinimg.com/736x/da/fb/68/dafb68812fdbb888b17da76e31771676.jpg</t>
-  </si>
-  <si>
     <t>https://i.pinimg.com/736x/2e/81/bb/2e81bb84ded9279f3f85c133d864c007.jpg</t>
   </si>
   <si>
     <t>https://i.pinimg.com/736x/ea/d8/f7/ead8f7ca5d4e1bccbaac0fba1a71fa46.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1c15C82GH-mpahXobD81y8HzDnI11IMZg/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1SyWMkZZ6mHPUl-VDVWEbejmYIbUNDG5F/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Kph7afQ9k2W_bQq6tSRWi0_Rj4lURmCL/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -918,13 +843,13 @@
     </row>
     <row r="2" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
         <v>35</v>
@@ -978,7 +903,7 @@
         <v>2016</v>
       </c>
       <c r="U2">
-        <v>61</v>
+        <v>61.436300000000003</v>
       </c>
       <c r="V2" t="s">
         <v>46</v>
@@ -990,7 +915,7 @@
         <v>48</v>
       </c>
       <c r="Y2">
-        <v>66</v>
+        <v>66.348500000000001</v>
       </c>
       <c r="Z2" t="s">
         <v>49</v>
@@ -1014,24 +939,24 @@
         <v>55</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>58</v>
+        <v>77</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
         <v>59</v>
@@ -1085,7 +1010,7 @@
         <v>2016</v>
       </c>
       <c r="U3">
-        <v>62</v>
+        <v>62.343200000000003</v>
       </c>
       <c r="V3" t="s">
         <v>46</v>
@@ -1097,7 +1022,7 @@
         <v>48</v>
       </c>
       <c r="Y3">
-        <v>65</v>
+        <v>65.385499999999993</v>
       </c>
       <c r="Z3" t="s">
         <v>49</v>
@@ -1121,10 +1046,10 @@
         <v>55</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>57</v>
+        <v>88</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="AI3" t="s">
         <v>58</v>
@@ -1132,28 +1057,28 @@
     </row>
     <row r="4" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
         <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
         <v>38</v>
       </c>
       <c r="H4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
         <v>40</v>
@@ -1165,7 +1090,7 @@
         <v>2010</v>
       </c>
       <c r="L4">
-        <v>86.9</v>
+        <v>87.67</v>
       </c>
       <c r="M4" t="s">
         <v>42</v>
@@ -1177,7 +1102,7 @@
         <v>2012</v>
       </c>
       <c r="P4">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q4" t="s">
         <v>43</v>
@@ -1186,34 +1111,34 @@
         <v>44</v>
       </c>
       <c r="S4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="T4">
         <v>2016</v>
       </c>
       <c r="U4">
-        <v>63</v>
+        <v>64.345299999999995</v>
       </c>
       <c r="V4" t="s">
         <v>46</v>
       </c>
       <c r="W4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="X4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="Y4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="Z4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="AA4" t="s">
         <v>50</v>
       </c>
       <c r="AB4" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="AC4" t="s">
         <v>52</v>
@@ -1228,7 +1153,7 @@
         <v>55</v>
       </c>
       <c r="AG4" s="1" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="AH4" t="s">
         <v>57</v>
@@ -1239,28 +1164,28 @@
     </row>
     <row r="5" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" t="s">
         <v>67</v>
-      </c>
-      <c r="D5" t="s">
-        <v>68</v>
       </c>
       <c r="E5" t="s">
         <v>36</v>
       </c>
       <c r="F5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" t="s">
         <v>69</v>
-      </c>
-      <c r="G5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" t="s">
-        <v>70</v>
       </c>
       <c r="I5" t="s">
         <v>40</v>
@@ -1272,7 +1197,7 @@
         <v>2010</v>
       </c>
       <c r="L5">
-        <v>87.67</v>
+        <v>88.3</v>
       </c>
       <c r="M5" t="s">
         <v>42</v>
@@ -1284,7 +1209,7 @@
         <v>2012</v>
       </c>
       <c r="P5">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="Q5" t="s">
         <v>43</v>
@@ -1299,28 +1224,28 @@
         <v>2016</v>
       </c>
       <c r="U5">
-        <v>64</v>
+        <v>65.3523</v>
       </c>
       <c r="V5" t="s">
         <v>46</v>
       </c>
       <c r="W5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="X5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="Y5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="Z5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="AA5" t="s">
         <v>50</v>
       </c>
       <c r="AB5" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="AC5" t="s">
         <v>52</v>
@@ -1335,7 +1260,7 @@
         <v>55</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="AH5" t="s">
         <v>57</v>
@@ -1346,16 +1271,16 @@
     </row>
     <row r="6" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
         <v>36</v>
@@ -1364,10 +1289,10 @@
         <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I6" t="s">
         <v>40</v>
@@ -1379,7 +1304,7 @@
         <v>2010</v>
       </c>
       <c r="L6">
-        <v>88.3</v>
+        <v>82.45</v>
       </c>
       <c r="M6" t="s">
         <v>42</v>
@@ -1391,7 +1316,7 @@
         <v>2012</v>
       </c>
       <c r="P6">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q6" t="s">
         <v>43</v>
@@ -1406,25 +1331,25 @@
         <v>2016</v>
       </c>
       <c r="U6">
-        <v>65</v>
+        <v>67.339399999999998</v>
       </c>
       <c r="V6" t="s">
         <v>46</v>
       </c>
       <c r="W6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="X6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="Y6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="Z6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="AA6" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="AB6" t="s">
         <v>51</v>
@@ -1441,8 +1366,8 @@
       <c r="AF6" t="s">
         <v>55</v>
       </c>
-      <c r="AG6" s="1" t="s">
-        <v>118</v>
+      <c r="AG6" t="s">
+        <v>56</v>
       </c>
       <c r="AH6" t="s">
         <v>57</v>
@@ -1451,557 +1376,29 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7">
-        <v>2010</v>
-      </c>
-      <c r="L7">
-        <v>81.89</v>
-      </c>
-      <c r="M7" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7">
-        <v>2012</v>
-      </c>
-      <c r="P7">
-        <v>80</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>43</v>
-      </c>
-      <c r="R7" t="s">
-        <v>44</v>
-      </c>
-      <c r="S7" t="s">
-        <v>45</v>
-      </c>
-      <c r="T7">
-        <v>2016</v>
-      </c>
-      <c r="U7">
-        <v>66</v>
-      </c>
-      <c r="V7" t="s">
-        <v>46</v>
-      </c>
-      <c r="W7" t="s">
-        <v>66</v>
-      </c>
-      <c r="X7" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>53</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>58</v>
-      </c>
+    <row r="7" spans="1:35" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C8" s="1"/>
     </row>
-    <row r="8" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>101</v>
-      </c>
-      <c r="B8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" t="s">
-        <v>78</v>
-      </c>
-      <c r="I8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8">
-        <v>2010</v>
-      </c>
-      <c r="L8">
-        <v>82.45</v>
-      </c>
-      <c r="M8" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8" t="s">
-        <v>41</v>
-      </c>
-      <c r="O8">
-        <v>2012</v>
-      </c>
-      <c r="P8">
-        <v>85</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>43</v>
-      </c>
-      <c r="R8" t="s">
-        <v>44</v>
-      </c>
-      <c r="S8" t="s">
-        <v>45</v>
-      </c>
-      <c r="T8">
-        <v>2016</v>
-      </c>
-      <c r="U8">
-        <v>67</v>
-      </c>
-      <c r="V8" t="s">
-        <v>46</v>
-      </c>
-      <c r="W8" t="s">
-        <v>66</v>
-      </c>
-      <c r="X8" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>53</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" t="s">
-        <v>82</v>
-      </c>
-      <c r="I9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9">
-        <v>2010</v>
-      </c>
-      <c r="L9">
-        <v>84</v>
-      </c>
-      <c r="M9" t="s">
-        <v>42</v>
-      </c>
-      <c r="N9" t="s">
-        <v>41</v>
-      </c>
-      <c r="O9">
-        <v>2012</v>
-      </c>
-      <c r="P9">
-        <v>89</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>43</v>
-      </c>
-      <c r="R9" t="s">
-        <v>44</v>
-      </c>
-      <c r="S9" t="s">
-        <v>45</v>
-      </c>
-      <c r="T9">
-        <v>2016</v>
-      </c>
-      <c r="U9">
-        <v>68</v>
-      </c>
-      <c r="V9" t="s">
-        <v>46</v>
-      </c>
-      <c r="W9" t="s">
-        <v>66</v>
-      </c>
-      <c r="X9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>53</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10">
-        <v>2010</v>
-      </c>
-      <c r="L10">
-        <v>85.5</v>
-      </c>
-      <c r="M10" t="s">
-        <v>42</v>
-      </c>
-      <c r="N10" t="s">
-        <v>41</v>
-      </c>
-      <c r="O10">
-        <v>2012</v>
-      </c>
-      <c r="P10">
-        <v>91</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>43</v>
-      </c>
-      <c r="R10" t="s">
-        <v>44</v>
-      </c>
-      <c r="S10" t="s">
-        <v>45</v>
-      </c>
-      <c r="T10">
-        <v>2016</v>
-      </c>
-      <c r="U10">
-        <v>69</v>
-      </c>
-      <c r="V10" t="s">
-        <v>46</v>
-      </c>
-      <c r="W10" t="s">
-        <v>66</v>
-      </c>
-      <c r="X10" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>53</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" t="s">
-        <v>89</v>
-      </c>
-      <c r="I11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11">
-        <v>2010</v>
-      </c>
-      <c r="L11">
-        <v>86</v>
-      </c>
-      <c r="M11" t="s">
-        <v>42</v>
-      </c>
-      <c r="N11" t="s">
-        <v>41</v>
-      </c>
-      <c r="O11">
-        <v>2012</v>
-      </c>
-      <c r="P11">
-        <v>85</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>43</v>
-      </c>
-      <c r="R11" t="s">
-        <v>44</v>
-      </c>
-      <c r="S11" t="s">
-        <v>45</v>
-      </c>
-      <c r="T11">
-        <v>2016</v>
-      </c>
-      <c r="U11">
-        <v>66.5</v>
-      </c>
-      <c r="V11" t="s">
-        <v>46</v>
-      </c>
-      <c r="W11" t="s">
-        <v>66</v>
-      </c>
-      <c r="X11" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>53</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>58</v>
-      </c>
-    </row>
+    <row r="9" spans="1:35" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:35" ht="15.6" x14ac:dyDescent="0.3"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{4C013530-CFB1-446E-A071-309B010AB571}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{E1E5B070-B26C-44B6-8C7F-41CC7815889B}"/>
-    <hyperlink ref="C6" r:id="rId3" xr:uid="{781C2549-5C75-4FAF-AE8F-67254D7CF271}"/>
-    <hyperlink ref="C8" r:id="rId4" xr:uid="{977E7F97-BEAA-4529-8132-3F0AFC3E1A06}"/>
-    <hyperlink ref="C10" r:id="rId5" xr:uid="{28840397-27B4-4FCF-9254-DF47AE4E78FA}"/>
-    <hyperlink ref="AG2" r:id="rId6" xr:uid="{31598430-12C5-495F-9888-CC381B103D17}"/>
-    <hyperlink ref="AG3" r:id="rId7" xr:uid="{1700339A-A0CD-4963-9323-6830F89EE3F9}"/>
-    <hyperlink ref="AG4" r:id="rId8" xr:uid="{45327DEF-E0F1-4C1C-B2CE-0123C9FE1A86}"/>
-    <hyperlink ref="AG5" r:id="rId9" xr:uid="{9C06E931-234B-4D4E-8E76-E65B80EDDD3D}"/>
-    <hyperlink ref="AG6" r:id="rId10" xr:uid="{D73C8EFE-CDCF-469B-A90A-DEF3AF8D57A6}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{781C2549-5C75-4FAF-AE8F-67254D7CF271}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{977E7F97-BEAA-4529-8132-3F0AFC3E1A06}"/>
+    <hyperlink ref="AG2" r:id="rId5" xr:uid="{31598430-12C5-495F-9888-CC381B103D17}"/>
+    <hyperlink ref="AG3" r:id="rId6" xr:uid="{1700339A-A0CD-4963-9323-6830F89EE3F9}"/>
+    <hyperlink ref="AG4" r:id="rId7" xr:uid="{9C06E931-234B-4D4E-8E76-E65B80EDDD3D}"/>
+    <hyperlink ref="AG5" r:id="rId8" xr:uid="{D73C8EFE-CDCF-469B-A90A-DEF3AF8D57A6}"/>
+    <hyperlink ref="AH2" r:id="rId9" xr:uid="{12B3DBA5-C7D3-4042-A469-331FA61B0C2D}"/>
+    <hyperlink ref="AH3" r:id="rId10" xr:uid="{14959D78-20F9-4279-A597-45299539B9D5}"/>
+    <hyperlink ref="AI2" r:id="rId11" xr:uid="{C45F4DEC-C075-49F8-B975-127F2D8F8C8D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AI1 C5:K5 D2:K2 D3:O3 C7:K7 D6:K6 C9:K9 D8:K8 C11:K11 D10:O10 AH2:AI2 C4:K4 Q3:T3 Q4:T4 Q5:T5 Q6:T6 Q7:T7 Q8:T8 Q9:T9 Q10:T10 Q11:T11 M2:T2 M4:O4 M5:O5 M6:O6 M7:O7 M8:O8 M9:O9 M11:O11 V2:X2 V3:X3 V4:AF4 V5:AF5 V6:AF6 V7:AI7 V8:AI8 V9:AI9 V10:AI10 V11:AI11 Z2:AF2 Z3:AF3 AH3:AI3 AH4:AI4 AH5:AI5 AH6:AI6" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AI1 C4:K4 D2:K2 D3:O3 D5:K5 D6:K6 Q3:T3 Q4:T4 Q5:T5 Q6:T6 M2:T2 M4:O4 M5:O5 M6:O6 V2:X2 V3:X3 V4:AF4 V5:AF5 V6:AI6 Z2:AF2 Z3:AF3 AI3 AH4:AI4 AH5:AI5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>